--- a/catalogo_1.xlsx
+++ b/catalogo_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Xenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A53E78B-46D0-4F57-A1AE-FB584DB394F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5FAA19-FA9C-42A6-ABEA-C18BAEB99037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7615,7 +7615,7 @@
     <t>EL VERDE</t>
   </si>
   <si>
-    <t>DISTRITO FEDERAL</t>
+    <t>CIUDAD DE MÉXICO</t>
   </si>
 </sst>
 </file>
@@ -7662,18 +7662,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">

--- a/catalogo_1.xlsx
+++ b/catalogo_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Xenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5FAA19-FA9C-42A6-ABEA-C18BAEB99037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F85FEF9-36ED-4D42-9861-F43A4C3F8F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="extrado_localizacin" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">extrado_localizacin!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">extrado_localizacin!$A$1:$D$6454</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
